--- a/data/TTN/最新版班表/TTN_TM.xlsx
+++ b/data/TTN/最新版班表/TTN_TM.xlsx
@@ -5314,12 +5314,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="L28" s="1" t="inlineStr">
-        <is>
-          <t>15:31
-NM0536
-23:31
-8:00</t>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>MLP</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -5950,18 +5947,18 @@
       </c>
       <c r="M31" s="1" t="inlineStr">
         <is>
-          <t>6:10
-NM0007
-14:10
+          <t>6:51
+NM0013
+14:51
 8:00</t>
         </is>
       </c>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>5:26
-NM0002
-15:01
-9:35</t>
+          <t>9:04
+NM0027
+17:06
+8:02</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
@@ -6374,10 +6371,10 @@
       </c>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>9:04
-NM0027
-17:06
-8:02</t>
+          <t>5:26
+NM0002
+15:01
+9:35</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr">
@@ -7627,17 +7624,17 @@
       </c>
       <c r="L39" s="1" t="inlineStr">
         <is>
-          <t>7:24
-NM0018
-15:24
+          <t>6:10
+NM0007
+14:10
 8:00</t>
         </is>
       </c>
       <c r="M39" s="1" t="inlineStr">
         <is>
-          <t>6:51
-NM0013
-14:51
+          <t>6:10
+NM0007
+14:10
 8:00</t>
         </is>
       </c>
@@ -11110,14 +11107,19 @@
       </c>
       <c r="Y55" s="1" t="inlineStr">
         <is>
-          <t>5:30
+          <t>16:56
 DO2W
-STD1
-13:30
-8:00</t>
-        </is>
-      </c>
-      <c r="Z55" s="1" t="inlineStr">
+NM5904
+24:56
+8:00</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="AA55" s="1" t="inlineStr">
         <is>
           <t>6:31
 NM0009
@@ -11125,17 +11127,12 @@
 9:35</t>
         </is>
       </c>
-      <c r="AA55" s="1" t="inlineStr">
+      <c r="AB55" s="1" t="inlineStr">
         <is>
           <t>6:31
 NM0009
 16:06
 9:35</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>DO3X</t>
         </is>
       </c>
       <c r="AC55" s="1" t="inlineStr">
@@ -12712,12 +12709,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="K63" s="1" t="inlineStr">
-        <is>
-          <t>16:30
-NM2547
-24:30
-8:00</t>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>NHS1</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -12929,9 +12923,9 @@
       </c>
       <c r="L64" s="1" t="inlineStr">
         <is>
-          <t>6:10
-NM0007
-14:10
+          <t>7:24
+NM0018
+15:24
 8:00</t>
         </is>
       </c>
@@ -14083,32 +14077,32 @@
       </c>
       <c r="Y69" s="1" t="inlineStr">
         <is>
-          <t>16:56
+          <t>5:30
 DO2W
-NM5904
-24:56
-8:00</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AA69" s="1" t="inlineStr">
-        <is>
-          <t>5:30
 STD1
 13:30
 8:00</t>
         </is>
       </c>
-      <c r="AB69" s="1" t="inlineStr">
+      <c r="Z69" s="1" t="inlineStr">
         <is>
           <t>6:31
 NM0009
 16:06
 9:35</t>
+        </is>
+      </c>
+      <c r="AA69" s="1" t="inlineStr">
+        <is>
+          <t>5:30
+STD1
+13:30
+8:00</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="AC69" s="1" t="inlineStr">
@@ -14380,7 +14374,14 @@
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+TTN1
+16:30
+8:00</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
@@ -14447,7 +14448,14 @@
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
+      <c r="L75" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+TTN1
+16:30
+8:00</t>
+        </is>
+      </c>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
@@ -14509,7 +14517,14 @@
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
+      <c r="M76" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+TTN1
+16:30
+8:00</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr"/>
@@ -14641,7 +14656,14 @@
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
+      <c r="M78" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+TTN1
+16:30
+8:00</t>
+        </is>
+      </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr"/>
@@ -14716,7 +14738,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+TTN1
+16:30
+8:00</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
